--- a/data-manipulation-scripts/sheets-cleanup/sheets/CUBO RODA - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CUBO RODA - 24_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -35,75 +35,6 @@
   </si>
   <si>
     <t>CUBO RODA TRASEIRO UNIBREQ YBR</t>
-  </si>
-  <si>
-    <t>7295991826644</t>
-  </si>
-  <si>
-    <t>RAIO INOX (FREIO A DISCO) IRON TITAN CG125-150 ESD 8292</t>
-  </si>
-  <si>
-    <t>7895099122633</t>
-  </si>
-  <si>
-    <t>RZ IRON POP100 024513</t>
-  </si>
-  <si>
-    <t>7895099126600</t>
-  </si>
-  <si>
-    <t>RAIO INOX IRON BROS NXR125-150 173287</t>
-  </si>
-  <si>
-    <t>602883764095</t>
-  </si>
-  <si>
-    <t>RAIO INOX IRON BROS NXR160/ XRE190 ESD DISCO 187240</t>
-  </si>
-  <si>
-    <t>7895099126594</t>
-  </si>
-  <si>
-    <t>RAIO INOX DISCO IRON NXR BROS150 173286</t>
-  </si>
-  <si>
-    <t>7895099126587</t>
-  </si>
-  <si>
-    <t>RAIO INOX IRON BROS NXR125-150 173285</t>
-  </si>
-  <si>
-    <t>RAIO SMARTFOX BROS NXR125</t>
-  </si>
-  <si>
-    <t>7908073702643</t>
-  </si>
-  <si>
-    <t>RAIO SMARTFOX CG TITAN125 2000 A 2004/ FAN150</t>
-  </si>
-  <si>
-    <t>7908073702322</t>
-  </si>
-  <si>
-    <t>RAIO SMARTFOX BROS NXR125-150</t>
-  </si>
-  <si>
-    <t>6941655608118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAIO INOX DISCO ALLEN </t>
-  </si>
-  <si>
-    <t>7899468024511</t>
-  </si>
-  <si>
-    <t>RAIO TRILHA CG TITAN150 KS/ FAN</t>
-  </si>
-  <si>
-    <t>3000000018316</t>
-  </si>
-  <si>
-    <t>RAIO SOLIDEZ BIZ125 30000</t>
   </si>
 </sst>
 </file>
@@ -438,160 +369,76 @@
       <c r="D5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>100.0</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>125.0</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>120.0</v>
-      </c>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>120.0</v>
-      </c>
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>120.0</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="3"/>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>120.0</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>50.0</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -6425,86 +6272,14 @@
       <c r="C989" s="4"/>
       <c r="D989" s="4"/>
     </row>
-    <row r="990">
-      <c r="A990" s="3"/>
-      <c r="B990" s="4"/>
-      <c r="C990" s="4"/>
-      <c r="D990" s="4"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="3"/>
-      <c r="B991" s="4"/>
-      <c r="C991" s="4"/>
-      <c r="D991" s="4"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="3"/>
-      <c r="B992" s="4"/>
-      <c r="C992" s="4"/>
-      <c r="D992" s="4"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="3"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="3"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="3"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="3"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="3"/>
-      <c r="B997" s="4"/>
-      <c r="C997" s="4"/>
-      <c r="D997" s="4"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="3"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="3"/>
-      <c r="B999" s="4"/>
-      <c r="C999" s="4"/>
-      <c r="D999" s="4"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="4"/>
-      <c r="C1000" s="4"/>
-      <c r="D1000" s="4"/>
-    </row>
-    <row r="1001">
-      <c r="A1001" s="3"/>
-      <c r="B1001" s="4"/>
-      <c r="C1001" s="4"/>
-      <c r="D1001" s="4"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1001">
+  <conditionalFormatting sqref="A1:A989">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1001">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A989">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/CUBO RODA - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CUBO RODA - 24_01.xlsx
@@ -338,7 +338,9 @@
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="2">
+        <v>200.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -360,7 +362,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="2">
+        <v>185.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
